--- a/outputs/evidences_Tests_Bayesian_Only.xlsx
+++ b/outputs/evidences_Tests_Bayesian_Only.xlsx
@@ -164,13 +164,13 @@
     <t xml:space="preserve">Chi-square</t>
   </si>
   <si>
-    <t xml:space="preserve">Cramer's V = 0.328</t>
+    <t xml:space="preserve">Cramer's V = 0.310</t>
   </si>
   <si>
     <t xml:space="preserve">Positive (more than expected; peak in Eastern Europe for 'Very Low')</t>
   </si>
   <si>
-    <t xml:space="preserve">Cramer's V = 0.276</t>
+    <t xml:space="preserve">Cramer's V = 0.278</t>
   </si>
   <si>
     <t xml:space="preserve">Positive (more than expected; peak in II for 'Very Low')</t>
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0000432688784842842</v>
+        <v>0.0000579070221820737</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0000137644381762808</v>
+        <v>0.0000149139601355441</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -603,7 +603,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.570515676927932</v>
+        <v>0.550381911522407</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0952201894069547</v>
+        <v>0.112802057466251</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -637,7 +637,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000234713730903229</v>
+        <v>0.000162862900883357</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.334840859501961</v>
+        <v>0.329890353657344</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -671,7 +671,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0170654336363501</v>
+        <v>0.0109649780994834</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -688,7 +688,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000000516850366672869</v>
+        <v>0.000000969282309616978</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -705,7 +705,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00441508270833222</v>
+        <v>0.00269693548895237</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -722,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0000121983654431574</v>
+        <v>0.0000180400032851624</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -739,7 +739,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>0.46509795187865</v>
+        <v>0.304070269717448</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -756,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00946656363417715</v>
+        <v>0.0153921365060855</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -773,7 +773,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0000173198618148041</v>
+        <v>0.0000137480249438618</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -790,7 +790,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.190341841034321</v>
+        <v>0.188482923832716</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -807,7 +807,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>0.570515676927932</v>
+        <v>0.550381911522407</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -824,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.356788937628764</v>
+        <v>0.37137551229008</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -841,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.497297437975968</v>
+        <v>0.465373239205258</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -858,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.770400415712889</v>
+        <v>0.758137131316928</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.29045098264249</v>
+        <v>3.33711906235957</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.750939261482638</v>
+        <v>0.40291148201269</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.1407586285883</v>
+        <v>-1.05777177069589</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.51312344975017</v>
+        <v>-2.52262489554756</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.573539334676404</v>
+        <v>-0.304572451936586</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1052,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.871268794196653</v>
+        <v>0.799600299750218</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -1075,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.04053196342894</v>
+        <v>1.05528970602217</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.306569669742483</v>
+        <v>0.319801074533416</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.164522549132125</v>
+        <v>0.190692517849119</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.51185789203691</v>
+        <v>-1.48718609731206</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.50004177051281</v>
+        <v>-1.47914799390689</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0961972140487763</v>
+        <v>0.125436301501063</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.200250469728704</v>
+        <v>-0.174077655955698</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.96467870299829</v>
+        <v>-2.02012600867102</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -1245,10 +1245,10 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.07465679081515</v>
+        <v>-1.05097357461806</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.69635217257507</v>
+        <v>1.55635754369867</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.92649614714391</v>
+        <v>2.97742452770542</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.1302889573695</v>
+        <v>2.16525095273312</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
@@ -1351,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.794719414239026</v>
+        <v>-0.797724035217466</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
@@ -1374,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.234146452895423</v>
+        <v>-0.241746889207614</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.125656172487509</v>
+        <v>-0.144149994031289</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1.15470053837925</v>
+        <v>1.1242070190744</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1443,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1.14567582649509</v>
+        <v>1.11813078403935</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0734718358370647</v>
+        <v>-0.0948209311861523</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.152943822580375</v>
+        <v>0.131590338991954</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
@@ -1512,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1.50054814545955</v>
+        <v>1.52707172455915</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1535,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.820782681668124</v>
+        <v>0.794461346554275</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.29561037268801</v>
+        <v>-1.176495717636</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
@@ -1581,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>-2.23514835254726</v>
+        <v>-2.25072138507785</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1604,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.62703506654572</v>
+        <v>-1.636775870565</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.305679770420355</v>
+        <v>0.301511344577763</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0318909915489958</v>
+        <v>0.076447078715644</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0944694930962273</v>
+        <v>-0.108711461300922</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -1696,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.959714869937393</v>
+        <v>-0.953462589245592</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -1719,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.100125234864352</v>
+        <v>-0.241746889207614</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.296597243432959</v>
+        <v>0.343775825476164</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0966644309165688</v>
+        <v>0.0953462589245593</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.136704149201289</v>
+        <v>0.134839972492648</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.305679770420355</v>
+        <v>0.301511344577763</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0601929265428846</v>
+        <v>-0.0656217958889712</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.103400116211468</v>
+        <v>0.0984731927834661</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.233629036188762</v>
+        <v>-0.237998648406575</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.334855411264458</v>
+        <v>0.330289129537908</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.02604030542914</v>
+        <v>-0.991601092815416</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.103400116211468</v>
+        <v>0.0984731927834661</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.162743034763439</v>
+        <v>0.174991455703923</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.386657723666275</v>
+        <v>0.381385035698237</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.255750044830824</v>
+        <v>0.252262489554757</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.303488489333442</v>
+        <v>-0.301511344577764</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.429197537639476</v>
+        <v>-0.426401432711221</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.959714869937393</v>
+        <v>-0.953462589245592</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2110,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.188982236504614</v>
+        <v>0.207514339159822</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.324635905558743</v>
+        <v>-0.311399577664609</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.73350375712192</v>
+        <v>0.752617809006382</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.05131496607569</v>
+        <v>-1.04446593573419</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>3.22136508059179</v>
+        <v>3.13571798360874</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -2225,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.324635905558743</v>
+        <v>-0.311399577664609</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.510949449570805</v>
+        <v>-0.55337157109286</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.21395395733377</v>
+        <v>-1.20604537831105</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.802955068546966</v>
+        <v>-0.797724035217466</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.70952622929136</v>
+        <v>-1.71674336818518</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.879441068138325</v>
+        <v>0.935819200357407</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.206943890199911</v>
+        <v>0.169035776015296</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>3.18476442742699</v>
+        <v>3.22519919615069</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.63835604381825</v>
+        <v>-1.75809814598307</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
@@ -2432,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.38552642755018</v>
+        <v>-0.317562927009622</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.881087844357011</v>
+        <v>-0.88273482950475</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.359030312631185</v>
+        <v>0.353706410895003</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.802816185026331</v>
+        <v>0.7909115788387</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.455661188432884</v>
+        <v>-0.469155716043788</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.188937275524615</v>
+        <v>-0.201330351745361</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.65855590190579</v>
+        <v>-0.669192683626209</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.551806160400518</v>
+        <v>0.539376610938154</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.146319704219894</v>
+        <v>-0.108870628972252</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.397153864878272</v>
+        <v>0.383667274080781</v>
       </c>
       <c r="D76" t="s">
         <v>13</v>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.00703981005159206</v>
+        <v>0.0506283146809843</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.164270615049612</v>
+        <v>0.150800533373728</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.186265369344385</v>
+        <v>-0.194624736040381</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -2731,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>1.64142390802024</v>
+        <v>1.65836997846835</v>
       </c>
       <c r="D80" t="s">
         <v>13</v>
@@ -2754,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.668856054059939</v>
+        <v>-0.664498639244989</v>
       </c>
       <c r="D81" t="s">
         <v>13</v>
@@ -2777,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.4956076040403</v>
+        <v>-1.4858641283079</v>
       </c>
       <c r="D82" t="s">
         <v>13</v>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>0.848874687627165</v>
+        <v>0.881390117064201</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
@@ -2823,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>0.351980978001836</v>
+        <v>0.378233870386986</v>
       </c>
       <c r="D84" t="s">
         <v>13</v>
@@ -2846,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>1.22685769538093</v>
+        <v>1.25719414170957</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -2869,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>-1.02798810592518</v>
+        <v>-1.01331220743797</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>0.272586510254553</v>
+        <v>0.204532297344429</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
@@ -2915,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.73987838233039</v>
+        <v>-0.720785300171427</v>
       </c>
       <c r="D88" t="s">
         <v>13</v>
@@ -2938,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.0131148245894105</v>
+        <v>-0.0951140414098058</v>
       </c>
       <c r="D89" t="s">
         <v>13</v>
@@ -2961,7 +2961,7 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.306028186241061</v>
+        <v>-0.283304871321676</v>
       </c>
       <c r="D90" t="s">
         <v>13</v>
@@ -2984,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.347003346415717</v>
+        <v>0.365636212063565</v>
       </c>
       <c r="D91" t="s">
         <v>13</v>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>1.87250070506513</v>
+        <v>1.82981497146618</v>
       </c>
       <c r="D92" t="s">
         <v>15</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.479053911940276</v>
+        <v>0.795471633445986</v>
       </c>
       <c r="D93" t="s">
         <v>15</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.664885280938959</v>
+        <v>-0.76854535950023</v>
       </c>
       <c r="D94" t="s">
         <v>15</v>
@@ -3076,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.82385600918499</v>
+        <v>-1.8062034664929</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
@@ -3099,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.466608826182237</v>
+        <v>-0.785207053298757</v>
       </c>
       <c r="D96" t="s">
         <v>15</v>
@@ -3122,7 +3122,7 @@
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0.647612581281775</v>
+        <v>0.758628229702405</v>
       </c>
       <c r="D97" t="s">
         <v>15</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.697740714924361</v>
+        <v>-0.702500173314209</v>
       </c>
       <c r="D98" t="s">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.98675438206593</v>
+        <v>-0.993485272670404</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>1.41928397390287</v>
+        <v>1.37966879637706</v>
       </c>
       <c r="D100" t="s">
         <v>15</v>
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.739795442874108</v>
+        <v>-0.776134749561287</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.258061122432908</v>
+        <v>0.219571031069952</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.925750450438767</v>
+        <v>-0.95368314501751</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.479053911940276</v>
+        <v>0.442945514815836</v>
       </c>
       <c r="D104" t="s">
         <v>15</v>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>-3.12566730665651</v>
+        <v>-2.94310598925321</v>
       </c>
       <c r="D105" t="s">
         <v>15</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.852088611806772</v>
+        <v>-0.883057407563938</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>2.44466175737055</v>
+        <v>2.48956884148894</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>1.50862857280943</v>
+        <v>1.46046088662691</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>1.40413720859062</v>
+        <v>1.36952476652465</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -3421,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>0.679614481492847</v>
+        <v>0.693435275171721</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
@@ -3444,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="C111" t="n">
-        <v>0.961120016912343</v>
+        <v>0.980665570775767</v>
       </c>
       <c r="D111" t="s">
         <v>15</v>
@@ -3467,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.38241315345869</v>
+        <v>-1.36186587249944</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
@@ -3490,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>0.720576692122892</v>
+        <v>0.766119688046888</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
@@ -3513,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.251357090340809</v>
+        <v>-0.216737737773667</v>
       </c>
       <c r="D114" t="s">
         <v>15</v>
@@ -3536,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>0.901700873848126</v>
+        <v>0.9413770404809</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
@@ -3559,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.466608826182237</v>
+        <v>-0.437229849358368</v>
       </c>
       <c r="D116" t="s">
         <v>15</v>
@@ -3582,7 +3582,7 @@
         <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>3.0444672648389</v>
+        <v>2.90512883703521</v>
       </c>
       <c r="D117" t="s">
         <v>15</v>
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>0.829952656785689</v>
+        <v>0.871662641046271</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>-2.3811531950531</v>
+        <v>-2.45744402668592</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>-1.46943671674129</v>
+        <v>-1.44161544048858</v>
       </c>
       <c r="D120" t="s">
         <v>15</v>
@@ -3674,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>-1.36765987787394</v>
+        <v>-1.35185273883875</v>
       </c>
       <c r="D121" t="s">
         <v>15</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>2.02345730550128</v>
+        <v>1.98590716225111</v>
       </c>
       <c r="D122" t="s">
         <v>16</v>
@@ -3706,10 +3706,10 @@
         <v>6</v>
       </c>
       <c r="F122" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0.634797050072037</v>
+        <v>0.893569579634018</v>
       </c>
       <c r="D123" t="s">
         <v>16</v>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.754071271022426</v>
+        <v>-0.844029862488261</v>
       </c>
       <c r="D124" t="s">
         <v>16</v>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>-2.16126181467654</v>
+        <v>-2.14718178326606</v>
       </c>
       <c r="D125" t="s">
         <v>16</v>
@@ -3789,7 +3789,7 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.678028946130953</v>
+        <v>-0.966135960402093</v>
       </c>
       <c r="D126" t="s">
         <v>16</v>
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0.805426158078307</v>
+        <v>0.912573145268806</v>
       </c>
       <c r="D127" t="s">
         <v>16</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.729996395088431</v>
+        <v>-0.734139659030241</v>
       </c>
       <c r="D128" t="s">
         <v>16</v>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>-1.03237080241753</v>
+        <v>-1.03823026247653</v>
       </c>
       <c r="D129" t="s">
         <v>16</v>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.14249699334516</v>
+        <v>-0.167823140471925</v>
       </c>
       <c r="D130" t="s">
         <v>16</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.353553390593274</v>
+        <v>-0.387576253376171</v>
       </c>
       <c r="D131" t="s">
         <v>16</v>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.356025822047941</v>
+        <v>0.322013497930319</v>
       </c>
       <c r="D132" t="s">
         <v>16</v>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.732371846139407</v>
+        <v>-0.758031750557388</v>
       </c>
       <c r="D133" t="s">
         <v>16</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.156097635263616</v>
+        <v>-0.183841039415663</v>
       </c>
       <c r="D134" t="s">
         <v>16</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>-2.45774337366514</v>
+        <v>-2.30855965068546</v>
       </c>
       <c r="D135" t="s">
         <v>16</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.705070745624354</v>
+        <v>-0.73309455911796</v>
       </c>
       <c r="D136" t="s">
         <v>16</v>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>1.74610864112594</v>
+        <v>1.79989600389876</v>
       </c>
       <c r="D137" t="s">
         <v>16</v>
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>2.55949353339648</v>
+        <v>2.51199594174203</v>
       </c>
       <c r="D138" t="s">
         <v>16</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>1.17518373401285</v>
+        <v>1.14668912414223</v>
       </c>
       <c r="D139" t="s">
         <v>16</v>
@@ -4111,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0.779711699014726</v>
+        <v>0.793758808169083</v>
       </c>
       <c r="D140" t="s">
         <v>16</v>
@@ -4134,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>1.10267885948759</v>
+        <v>1.12254447176582</v>
       </c>
       <c r="D141" t="s">
         <v>16</v>
@@ -4157,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.152201536244827</v>
+        <v>0.181451981684456</v>
       </c>
       <c r="D142" t="s">
         <v>16</v>
@@ -4180,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.37763161123351</v>
+        <v>0.419051145337777</v>
       </c>
       <c r="D143" t="s">
         <v>16</v>
@@ -4203,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.380272423904897</v>
+        <v>-0.348164068222608</v>
       </c>
       <c r="D144" t="s">
         <v>16</v>
@@ -4226,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.782248926578237</v>
+        <v>0.819591165625846</v>
       </c>
       <c r="D145" t="s">
         <v>16</v>
@@ -4249,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.166728429376464</v>
+        <v>0.198770686945181</v>
       </c>
       <c r="D146" t="s">
         <v>16</v>
@@ -4272,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>2.62512428077194</v>
+        <v>2.49603673412206</v>
       </c>
       <c r="D147" t="s">
         <v>16</v>
@@ -4295,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="C148" t="n">
-        <v>0.753088525772443</v>
+        <v>0.792628836166363</v>
       </c>
       <c r="D148" t="s">
         <v>16</v>
@@ -4318,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.86502473765186</v>
+        <v>-1.94606474300842</v>
       </c>
       <c r="D149" t="s">
         <v>16</v>
@@ -4341,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>-2.73380398173064</v>
+        <v>-2.7159939942171</v>
       </c>
       <c r="D150" t="s">
         <v>16</v>
@@ -4364,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.25521785048079</v>
+        <v>-1.23981122845468</v>
       </c>
       <c r="D151" t="s">
         <v>16</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.427862549840558</v>
+        <v>-0.446811800143156</v>
       </c>
       <c r="D152" t="s">
         <v>17</v>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0.644462417663218</v>
+        <v>0.839660058321016</v>
       </c>
       <c r="D153" t="s">
         <v>17</v>
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.0771340181150455</v>
+        <v>-0.151623798202213</v>
       </c>
       <c r="D154" t="s">
         <v>17</v>
@@ -4456,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.529812942826018</v>
+        <v>0.559258940715804</v>
       </c>
       <c r="D155" t="s">
         <v>17</v>
@@ -4479,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.798023875121013</v>
+        <v>-1.05097357461806</v>
       </c>
       <c r="D156" t="s">
         <v>17</v>
@@ -4502,7 +4502,7 @@
         <v>1</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0955133865881836</v>
+        <v>0.189782285836471</v>
       </c>
       <c r="D157" t="s">
         <v>17</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>0.507382568618804</v>
+        <v>0.498685755491408</v>
       </c>
       <c r="D158" t="s">
         <v>17</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.191345949293976</v>
+        <v>-0.199820311653829</v>
       </c>
       <c r="D159" t="s">
         <v>17</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>0.791545717205033</v>
+        <v>0.767464974363539</v>
       </c>
       <c r="D160" t="s">
         <v>17</v>
@@ -4594,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.737209780774486</v>
+        <v>-0.762709057112379</v>
       </c>
       <c r="D161" t="s">
         <v>17</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.358082016778131</v>
+        <v>-0.381988321588463</v>
       </c>
       <c r="D162" t="s">
         <v>17</v>
@@ -4640,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0469075350623519</v>
+        <v>0.0230517572021508</v>
       </c>
       <c r="D163" t="s">
         <v>17</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>0.644462417663218</v>
+        <v>0.619020163624091</v>
       </c>
       <c r="D164" t="s">
         <v>17</v>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>-2.23709111549774</v>
+        <v>-2.11442760328357</v>
       </c>
       <c r="D165" t="s">
         <v>17</v>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>0.969441557618841</v>
+        <v>0.939948791324422</v>
       </c>
       <c r="D166" t="s">
         <v>17</v>
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0318909915489958</v>
+        <v>0.118219903852419</v>
       </c>
       <c r="D167" t="s">
         <v>17</v>
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>1.06550339409949</v>
+        <v>1.03477294264467</v>
       </c>
       <c r="D168" t="s">
         <v>17</v>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0.856584213723932</v>
+        <v>0.835619044553731</v>
       </c>
       <c r="D169" t="s">
         <v>17</v>
@@ -4801,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.628280862437543</v>
+        <v>-0.624187783932359</v>
       </c>
       <c r="D170" t="s">
         <v>17</v>
@@ -4824,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="C171" t="n">
-        <v>0.236939551103637</v>
+        <v>0.250108201693012</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -4847,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.980153944228132</v>
+        <v>-0.960609474641263</v>
       </c>
       <c r="D172" t="s">
         <v>17</v>
@@ -4870,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>0.912870929175277</v>
+        <v>0.954656656825879</v>
       </c>
       <c r="D173" t="s">
         <v>17</v>
@@ -4893,7 +4893,7 @@
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>0.443405217757417</v>
+        <v>0.478121625321725</v>
       </c>
       <c r="D174" t="s">
         <v>17</v>
@@ -4916,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.058084586279777</v>
+        <v>-0.0288530905190557</v>
       </c>
       <c r="D175" t="s">
         <v>17</v>
@@ -4939,7 +4939,7 @@
         <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.798023875121013</v>
+        <v>-0.774806217918181</v>
       </c>
       <c r="D176" t="s">
         <v>17</v>
@@ -4962,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>2.77014155062992</v>
+        <v>2.6465562038732</v>
       </c>
       <c r="D177" t="s">
         <v>17</v>
@@ -4985,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>-1.20043851636764</v>
+        <v>-1.17650152747706</v>
       </c>
       <c r="D178" t="s">
         <v>17</v>
@@ -5008,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.0394899251839396</v>
+        <v>-0.147971781808011</v>
       </c>
       <c r="D179" t="s">
         <v>17</v>
@@ -5031,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>-1.31938981111884</v>
+        <v>-1.29518965165965</v>
       </c>
       <c r="D180" t="s">
         <v>17</v>
@@ -5054,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>-1.06068970799268</v>
+        <v>-1.04591557687004</v>
       </c>
       <c r="D181" t="s">
         <v>17</v>
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.35372469757586</v>
+        <v>-1.35680105059994</v>
       </c>
       <c r="D182" t="s">
         <v>19</v>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>0.334855411264458</v>
+        <v>0.356753034006338</v>
       </c>
       <c r="D183" t="s">
         <v>19</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0.273719300509581</v>
+        <v>0.259235023102198</v>
       </c>
       <c r="D184" t="s">
         <v>19</v>
@@ -5146,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>4.25016585257988</v>
+        <v>4.29058165160516</v>
       </c>
       <c r="D185" t="s">
         <v>19</v>
@@ -5169,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>-1.05131496607569</v>
+        <v>-1.12815214963553</v>
       </c>
       <c r="D186" t="s">
         <v>19</v>
@@ -5192,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.859371500203189</v>
+        <v>-0.819773122289315</v>
       </c>
       <c r="D187" t="s">
         <v>19</v>
@@ -5215,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0966644309165688</v>
+        <v>0.0953462589245593</v>
       </c>
       <c r="D188" t="s">
         <v>19</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.605404089319993</v>
+        <v>-0.606779876216918</v>
       </c>
       <c r="D189" t="s">
         <v>19</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.305679770420355</v>
+        <v>0.301511344577763</v>
       </c>
       <c r="D190" t="s">
         <v>19</v>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.0601929265428846</v>
+        <v>-0.0656217958889712</v>
       </c>
       <c r="D191" t="s">
         <v>19</v>
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>0.103400116211468</v>
+        <v>0.0984731927834661</v>
       </c>
       <c r="D192" t="s">
         <v>19</v>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0574497629972367</v>
+        <v>0.0528885885347945</v>
       </c>
       <c r="D193" t="s">
         <v>19</v>
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>0.334855411264458</v>
+        <v>0.330289129537908</v>
       </c>
       <c r="D194" t="s">
         <v>19</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>0.259328868405166</v>
+        <v>0.266969524988766</v>
       </c>
       <c r="D195" t="s">
         <v>19</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>0.374379731110488</v>
+        <v>0.369274472937998</v>
       </c>
       <c r="D196" t="s">
         <v>19</v>
@@ -5422,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.331995790917415</v>
+        <v>-0.306235047481865</v>
       </c>
       <c r="D197" t="s">
         <v>19</v>
@@ -5445,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.400466928082928</v>
+        <v>-0.405221600429377</v>
       </c>
       <c r="D198" t="s">
         <v>19</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.537597033011733</v>
+        <v>-0.540562477617335</v>
       </c>
       <c r="D199" t="s">
         <v>19</v>
@@ -5491,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.303488489333442</v>
+        <v>-0.301511344577764</v>
       </c>
       <c r="D200" t="s">
         <v>19</v>
@@ -5514,7 +5514,7 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>1.90073195240339</v>
+        <v>1.91880644720049</v>
       </c>
       <c r="D201" t="s">
         <v>19</v>
@@ -5537,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.959714869937393</v>
+        <v>-0.953462589245592</v>
       </c>
       <c r="D202" t="s">
         <v>19</v>
@@ -5560,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>0.188982236504614</v>
+        <v>0.207514339159822</v>
       </c>
       <c r="D203" t="s">
         <v>19</v>
@@ -5583,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.324635905558743</v>
+        <v>-0.311399577664609</v>
       </c>
       <c r="D204" t="s">
         <v>19</v>
@@ -5606,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.180369776341456</v>
+        <v>-0.167248402001418</v>
       </c>
       <c r="D205" t="s">
         <v>19</v>
@@ -5629,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>-1.05131496607569</v>
+        <v>-1.04446593573419</v>
       </c>
       <c r="D206" t="s">
         <v>19</v>
@@ -5652,7 +5652,7 @@
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.814191174215507</v>
+        <v>-0.844231764817738</v>
       </c>
       <c r="D207" t="s">
         <v>19</v>
@@ -5675,7 +5675,7 @@
         <v>1</v>
       </c>
       <c r="C208" t="n">
-        <v>-1.17540586495407</v>
+        <v>-1.16774841624228</v>
       </c>
       <c r="D208" t="s">
         <v>19</v>
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>1.04233687712444</v>
+        <v>0.968400249412504</v>
       </c>
       <c r="D209" t="s">
         <v>19</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>1.25730945580997</v>
+        <v>1.2814232144555</v>
       </c>
       <c r="D210" t="s">
         <v>19</v>
@@ -5744,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="C211" t="n">
-        <v>1.68784432776199</v>
+        <v>1.70940864689457</v>
       </c>
       <c r="D211" t="s">
         <v>19</v>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>0.305679770420355</v>
+        <v>0.301511344577763</v>
       </c>
       <c r="D212" t="s">
         <v>21</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>0.0318909915489958</v>
+        <v>0.076447078715644</v>
       </c>
       <c r="D213" t="s">
         <v>21</v>
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.0944694930962273</v>
+        <v>-0.108711461300922</v>
       </c>
       <c r="D214" t="s">
         <v>21</v>
@@ -5836,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.959714869937393</v>
+        <v>-0.953462589245592</v>
       </c>
       <c r="D215" t="s">
         <v>21</v>
@@ -5859,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.100125234864352</v>
+        <v>-0.241746889207614</v>
       </c>
       <c r="D216" t="s">
         <v>21</v>
@@ -5882,7 +5882,7 @@
         <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>0.296597243432959</v>
+        <v>0.343775825476164</v>
       </c>
       <c r="D217" t="s">
         <v>21</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>0.0966644309165688</v>
+        <v>0.0953462589245593</v>
       </c>
       <c r="D218" t="s">
         <v>21</v>
@@ -5928,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>0.136704149201289</v>
+        <v>0.134839972492648</v>
       </c>
       <c r="D219" t="s">
         <v>21</v>
@@ -5951,7 +5951,7 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>0.305679770420355</v>
+        <v>0.301511344577763</v>
       </c>
       <c r="D220" t="s">
         <v>21</v>
@@ -5974,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.0601929265428846</v>
+        <v>-0.0656217958889712</v>
       </c>
       <c r="D221" t="s">
         <v>21</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>0.374379731110488</v>
+        <v>0.369274472937998</v>
       </c>
       <c r="D222" t="s">
         <v>21</v>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>0.348528562183235</v>
+        <v>0.343775825476164</v>
       </c>
       <c r="D223" t="s">
         <v>21</v>
@@ -6043,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>0.334855411264458</v>
+        <v>0.330289129537908</v>
       </c>
       <c r="D224" t="s">
         <v>21</v>
@@ -6066,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.597583914151036</v>
+        <v>-0.572077553547355</v>
       </c>
       <c r="D225" t="s">
         <v>21</v>
@@ -6089,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.438559113586572</v>
+        <v>-0.443129367525598</v>
       </c>
       <c r="D226" t="s">
         <v>21</v>
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>0.162743034763439</v>
+        <v>0.174991455703923</v>
       </c>
       <c r="D227" t="s">
         <v>21</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.138092044166527</v>
+        <v>-0.143019388386839</v>
       </c>
       <c r="D228" t="s">
         <v>21</v>
@@ -6158,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.140923494090454</v>
+        <v>-0.144149994031289</v>
       </c>
       <c r="D229" t="s">
         <v>21</v>
@@ -6181,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.303488489333442</v>
+        <v>-0.301511344577764</v>
       </c>
       <c r="D230" t="s">
         <v>21</v>
@@ -6204,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.429197537639476</v>
+        <v>-0.426401432711221</v>
       </c>
       <c r="D231" t="s">
         <v>21</v>
@@ -6227,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.959714869937393</v>
+        <v>-0.953462589245592</v>
       </c>
       <c r="D232" t="s">
         <v>21</v>
@@ -6250,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="C233" t="n">
-        <v>0.188982236504614</v>
+        <v>0.207514339159822</v>
       </c>
       <c r="D233" t="s">
         <v>21</v>
@@ -6273,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>-1.17540586495407</v>
+        <v>-1.16774841624228</v>
       </c>
       <c r="D234" t="s">
         <v>21</v>
@@ -6296,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>-1.09424330980483</v>
+        <v>-1.08711461300922</v>
       </c>
       <c r="D235" t="s">
         <v>21</v>
@@ -6319,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>-1.05131496607569</v>
+        <v>-1.04446593573419</v>
       </c>
       <c r="D236" t="s">
         <v>21</v>
@@ -6342,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>1.87617966232269</v>
+        <v>1.80906806746658</v>
       </c>
       <c r="D237" t="s">
         <v>21</v>
@@ -6365,7 +6365,7 @@
         <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>1.37690401323191</v>
+        <v>1.40129809949074</v>
       </c>
       <c r="D238" t="s">
         <v>21</v>
@@ -6388,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.510949449570805</v>
+        <v>-0.55337157109286</v>
       </c>
       <c r="D239" t="s">
         <v>21</v>
@@ -6411,7 +6411,7 @@
         <v>1</v>
       </c>
       <c r="C240" t="n">
-        <v>0.43355498476206</v>
+        <v>0.452267016866645</v>
       </c>
       <c r="D240" t="s">
         <v>21</v>
@@ -6434,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>0.442444629607512</v>
+        <v>0.455842305838552</v>
       </c>
       <c r="D241" t="s">
         <v>21</v>
@@ -6457,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.977513715212119</v>
+        <v>-0.962984593510886</v>
       </c>
       <c r="D242" t="s">
         <v>22</v>
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.0449921270665848</v>
+        <v>-0.28968272975116</v>
       </c>
       <c r="D243" t="s">
         <v>22</v>
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>0.284783114307255</v>
+        <v>0.362147622360922</v>
       </c>
       <c r="D244" t="s">
         <v>22</v>
@@ -6526,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="C245" t="n">
-        <v>0.574269751558209</v>
+        <v>0.560793178695674</v>
       </c>
       <c r="D245" t="s">
         <v>22</v>
@@ -6549,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>0.0264319745396068</v>
+        <v>0.16869646713466</v>
       </c>
       <c r="D246" t="s">
         <v>22</v>
@@ -6572,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.16730438228758</v>
+        <v>-0.210896329670685</v>
       </c>
       <c r="D247" t="s">
         <v>22</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.506536225129478</v>
+        <v>-0.503236279740196</v>
       </c>
       <c r="D248" t="s">
         <v>22</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.716350399411379</v>
+        <v>-0.711683571886767</v>
       </c>
       <c r="D249" t="s">
         <v>22</v>
@@ -6641,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>0.271075231949579</v>
+        <v>0.293791909884677</v>
       </c>
       <c r="D250" t="s">
         <v>22</v>
@@ -6664,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.396296961950608</v>
+        <v>-0.370033078291309</v>
       </c>
       <c r="D251" t="s">
         <v>22</v>
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>0.586865151676952</v>
+        <v>0.616358564390793</v>
       </c>
       <c r="D252" t="s">
         <v>22</v>
@@ -6710,7 +6710,7 @@
         <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.183714909194871</v>
+        <v>-0.161045344107428</v>
       </c>
       <c r="D253" t="s">
         <v>22</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>1.0948084252869</v>
+        <v>1.12492522660698</v>
       </c>
       <c r="D254" t="s">
         <v>22</v>
@@ -6756,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.466608826182237</v>
+        <v>-0.529043268444822</v>
       </c>
       <c r="D255" t="s">
         <v>22</v>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>1.09659945484779</v>
+        <v>1.12943542339718</v>
       </c>
       <c r="D256" t="s">
         <v>22</v>
@@ -6802,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>0.177556936606239</v>
+        <v>0.0858476741635837</v>
       </c>
       <c r="D257" t="s">
         <v>22</v>
@@ -6825,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>-1.03904866693226</v>
+        <v>-1.01937605383271</v>
       </c>
       <c r="D258" t="s">
         <v>22</v>
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.593994266264839</v>
+        <v>-0.580370430699081</v>
       </c>
       <c r="D259" t="s">
         <v>22</v>
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>0.297579898505277</v>
+        <v>0.29305917753221</v>
       </c>
       <c r="D260" t="s">
         <v>22</v>
@@ -6894,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>0.420841528355771</v>
+        <v>0.414448263443956</v>
       </c>
       <c r="D261" t="s">
         <v>22</v>
@@ -6917,7 +6917,7 @@
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.159251275642192</v>
+        <v>-0.171089444347833</v>
       </c>
       <c r="D262" t="s">
         <v>22</v>
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>0.232816536833209</v>
+        <v>0.215488417567484</v>
       </c>
       <c r="D263" t="s">
         <v>22</v>
@@ -6963,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.344771535792274</v>
+        <v>-0.358935834353104</v>
       </c>
       <c r="D264" t="s">
         <v>22</v>
@@ -6986,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>0.107928833753482</v>
+        <v>0.0937846057400314</v>
       </c>
       <c r="D265" t="s">
         <v>22</v>
@@ -7009,7 +7009,7 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.643178047130428</v>
+        <v>-0.655099155142141</v>
       </c>
       <c r="D266" t="s">
         <v>22</v>
@@ -7032,7 +7032,7 @@
         <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>0.274123350410888</v>
+        <v>0.308087853303093</v>
       </c>
       <c r="D267" t="s">
         <v>22</v>
@@ -7055,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.644230241166135</v>
+        <v>-0.657725664030824</v>
       </c>
       <c r="D268" t="s">
         <v>22</v>
@@ -7078,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.104311148053995</v>
+        <v>-0.0499933128756567</v>
       </c>
       <c r="D269" t="s">
         <v>22</v>
@@ -7101,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>0.610420304626209</v>
+        <v>0.593632692949862</v>
       </c>
       <c r="D270" t="s">
         <v>22</v>
@@ -7124,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="C271" t="n">
-        <v>0.348959747987668</v>
+        <v>0.337978178307206</v>
       </c>
       <c r="D271" t="s">
         <v>22</v>
@@ -7178,7 +7178,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0444672648389</v>
+        <v>2.90512883703521</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -7195,7 +7195,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.3811531950531</v>
+        <v>-2.45744402668592</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -7212,7 +7212,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>2.62512428077194</v>
+        <v>2.49603673412206</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -7229,7 +7229,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.73380398173064</v>
+        <v>-2.7159939942171</v>
       </c>
       <c r="E5" t="s">
         <v>34</v>
@@ -7246,7 +7246,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>2.77014155062992</v>
+        <v>2.6465562038732</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -7263,7 +7263,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>3.22136508059179</v>
+        <v>3.13571798360874</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -7280,7 +7280,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.23514835254726</v>
+        <v>-2.25072138507785</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -7297,7 +7297,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>4.25016585257988</v>
+        <v>4.29058165160516</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -7314,7 +7314,7 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.16126181467654</v>
+        <v>-2.14718178326606</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
@@ -7331,7 +7331,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.51312344975017</v>
+        <v>-2.52262489554756</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
@@ -7348,7 +7348,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>3.18476442742699</v>
+        <v>3.22519919615069</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -7402,7 +7402,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000719075049296383</v>
+        <v>0.00025011441789534</v>
       </c>
       <c r="E2" t="s">
         <v>47</v>
@@ -7428,7 +7428,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.376681253265233</v>
+        <v>0.334001661035094</v>
       </c>
       <c r="E3" t="s">
         <v>49</v>
@@ -7491,7 +7491,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.276120108578258</v>
+        <v>0.436252187626311</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -7517,7 +7517,7 @@
         <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>0.48464900194837</v>
+        <v>0.473893510942743</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -7574,7 +7574,7 @@
         <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.725476250110012</v>
+        <v>-0.720749970156447</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -7597,7 +7597,7 @@
         <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>4.23850354260814</v>
+        <v>3.83761289440099</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -7620,7 +7620,7 @@
         <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.08653890939047</v>
+        <v>-1.05947039716904</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -7643,7 +7643,7 @@
         <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.00492746315953</v>
+        <v>-0.985329907499377</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -7666,7 +7666,7 @@
         <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.827430923219941</v>
+        <v>-1.08092801107506</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -7689,7 +7689,7 @@
         <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>0.530108291349522</v>
+        <v>0.628004153919412</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -7712,7 +7712,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2.59720497539384</v>
+        <v>2.51604243415518</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -7735,7 +7735,7 @@
         <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.476831648543416</v>
+        <v>0.125436301501063</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -7758,7 +7758,7 @@
         <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.575463200158657</v>
+        <v>-0.738988427584557</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -7781,7 +7781,7 @@
         <v>59</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.924804388989767</v>
+        <v>-0.918779540562285</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -7804,7 +7804,7 @@
         <v>59</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.01307245025896</v>
+        <v>-1.08711461300922</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -7827,7 +7827,7 @@
         <v>59</v>
       </c>
       <c r="C13" t="n">
-        <v>0.564288093646835</v>
+        <v>0.611576629725151</v>
       </c>
       <c r="D13" t="s">
         <v>56</v>
@@ -7850,7 +7850,7 @@
         <v>60</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.14707866935281</v>
+        <v>-1.13960576459638</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -7873,7 +7873,7 @@
         <v>60</v>
       </c>
       <c r="C15" t="n">
-        <v>0.335083126633356</v>
+        <v>0.134839972492648</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>
@@ -7896,7 +7896,7 @@
         <v>60</v>
       </c>
       <c r="C16" t="n">
-        <v>0.216336819411765</v>
+        <v>0.271820002733636</v>
       </c>
       <c r="D16" t="s">
         <v>56</v>
@@ -7919,7 +7919,7 @@
         <v>55</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.229415733870562</v>
+        <v>-0.227921152919276</v>
       </c>
       <c r="D17" t="s">
         <v>56</v>
@@ -7942,7 +7942,7 @@
         <v>55</v>
       </c>
       <c r="C18" t="n">
-        <v>2.75776415922296</v>
+        <v>2.78008922588756</v>
       </c>
       <c r="D18" t="s">
         <v>56</v>
@@ -7965,7 +7965,7 @@
         <v>55</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.725476250110012</v>
+        <v>-0.720749970156447</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -7988,7 +7988,7 @@
         <v>55</v>
       </c>
       <c r="C20" t="n">
-        <v>-1</v>
+        <v>-0.993485272670404</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -8011,7 +8011,7 @@
         <v>55</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.888523316638638</v>
+        <v>-0.88273482950475</v>
       </c>
       <c r="D21" t="s">
         <v>56</v>
@@ -8034,7 +8034,7 @@
         <v>55</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.827170191868511</v>
+        <v>-0.821781403613318</v>
       </c>
       <c r="D22" t="s">
         <v>56</v>
@@ -8057,7 +8057,7 @@
         <v>55</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.794719414239026</v>
+        <v>-0.789542033951723</v>
       </c>
       <c r="D23" t="s">
         <v>56</v>
@@ -8080,7 +8080,7 @@
         <v>55</v>
       </c>
       <c r="C24" t="n">
-        <v>0.655610068107186</v>
+        <v>0.615387112882045</v>
       </c>
       <c r="D24" t="s">
         <v>56</v>
@@ -8103,7 +8103,7 @@
         <v>55</v>
       </c>
       <c r="C25" t="n">
-        <v>0.236939551103637</v>
+        <v>0.250108201693012</v>
       </c>
       <c r="D25" t="s">
         <v>56</v>
@@ -8126,7 +8126,7 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>1.08147614087175</v>
+        <v>1.0196296219512</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
@@ -8149,7 +8149,7 @@
         <v>55</v>
       </c>
       <c r="C27" t="n">
-        <v>1.26178653628809</v>
+        <v>1.28205648517093</v>
       </c>
       <c r="D27" t="s">
         <v>56</v>
@@ -8172,7 +8172,7 @@
         <v>55</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.606976978666884</v>
+        <v>-0.603022689155527</v>
       </c>
       <c r="D28" t="s">
         <v>56</v>
@@ -8195,7 +8195,7 @@
         <v>57</v>
       </c>
       <c r="C29" t="n">
-        <v>0.945049770203775</v>
+        <v>0.959528040256418</v>
       </c>
       <c r="D29" t="s">
         <v>56</v>
@@ -8218,7 +8218,7 @@
         <v>57</v>
       </c>
       <c r="C30" t="n">
-        <v>0.220302560792267</v>
+        <v>0.23345850632394</v>
       </c>
       <c r="D30" t="s">
         <v>56</v>
@@ -8241,7 +8241,7 @@
         <v>57</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.505747808256758</v>
+        <v>-0.482876908310953</v>
       </c>
       <c r="D31" t="s">
         <v>56</v>
@@ -8264,7 +8264,7 @@
         <v>57</v>
       </c>
       <c r="C32" t="n">
-        <v>1.222232571574</v>
+        <v>1.26634401930938</v>
       </c>
       <c r="D32" t="s">
         <v>56</v>
@@ -8287,7 +8287,7 @@
         <v>57</v>
       </c>
       <c r="C33" t="n">
-        <v>0.399534169361992</v>
+        <v>0.434226872818308</v>
       </c>
       <c r="D33" t="s">
         <v>56</v>
@@ -8310,7 +8310,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0950507509239735</v>
+        <v>-0.0658159087146154</v>
       </c>
       <c r="D34" t="s">
         <v>56</v>
@@ -8333,7 +8333,7 @@
         <v>57</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0839422675730375</v>
+        <v>0.113179480369933</v>
       </c>
       <c r="D35" t="s">
         <v>56</v>
@@ -8356,7 +8356,7 @@
         <v>57</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.203506788442527</v>
+        <v>-0.286826661496005</v>
       </c>
       <c r="D36" t="s">
         <v>56</v>
@@ -8379,7 +8379,7 @@
         <v>57</v>
       </c>
       <c r="C37" t="n">
-        <v>0.807112650858789</v>
+        <v>0.844478028732538</v>
       </c>
       <c r="D37" t="s">
         <v>56</v>
@@ -8402,7 +8402,7 @@
         <v>57</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.19942505320235</v>
+        <v>-1.28528000464485</v>
       </c>
       <c r="D38" t="s">
         <v>56</v>
@@ -8425,7 +8425,7 @@
         <v>57</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.560798764736307</v>
+        <v>-0.531351549174253</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
@@ -8448,7 +8448,7 @@
         <v>57</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.482802355149396</v>
+        <v>-0.464058426867722</v>
       </c>
       <c r="D40" t="s">
         <v>56</v>
@@ -8471,7 +8471,7 @@
         <v>58</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.573539334676404</v>
+        <v>-0.581087203147976</v>
       </c>
       <c r="D41" t="s">
         <v>56</v>
@@ -8494,7 +8494,7 @@
         <v>58</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.811107105653813</v>
+        <v>-0.821781403613318</v>
       </c>
       <c r="D42" t="s">
         <v>56</v>
@@ -8517,7 +8517,7 @@
         <v>58</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.710966725107811</v>
+        <v>-0.749158702304633</v>
       </c>
       <c r="D43" t="s">
         <v>56</v>
@@ -8540,7 +8540,7 @@
         <v>58</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.9</v>
+        <v>-0.95368314501751</v>
       </c>
       <c r="D44" t="s">
         <v>56</v>
@@ -8563,7 +8563,7 @@
         <v>58</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.420567703208956</v>
+        <v>-0.473190684512516</v>
       </c>
       <c r="D45" t="s">
         <v>56</v>
@@ -8586,7 +8586,7 @@
         <v>58</v>
       </c>
       <c r="C46" t="n">
-        <v>0.349956619636678</v>
+        <v>0.291335994686099</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
@@ -8609,7 +8609,7 @@
         <v>58</v>
       </c>
       <c r="C47" t="n">
-        <v>0.026490647141301</v>
+        <v>-0.0258069887046252</v>
       </c>
       <c r="D47" t="s">
         <v>56</v>
@@ -8632,7 +8632,7 @@
         <v>58</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0374634324632679</v>
+        <v>0.1922057671951</v>
       </c>
       <c r="D48" t="s">
         <v>56</v>
@@ -8655,7 +8655,7 @@
         <v>58</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.420567703208956</v>
+        <v>-0.473190684512516</v>
       </c>
       <c r="D49" t="s">
         <v>56</v>
@@ -8678,7 +8678,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="n">
-        <v>1.26532708481995</v>
+        <v>1.4151427313163</v>
       </c>
       <c r="D50" t="s">
         <v>56</v>
@@ -8701,7 +8701,7 @@
         <v>58</v>
       </c>
       <c r="C51" t="n">
-        <v>0.757071921772854</v>
+        <v>0.687247365261549</v>
       </c>
       <c r="D51" t="s">
         <v>56</v>
@@ -8724,7 +8724,7 @@
         <v>58</v>
       </c>
       <c r="C52" t="n">
-        <v>0.459568283847783</v>
+        <v>0.413918677192358</v>
       </c>
       <c r="D52" t="s">
         <v>56</v>
@@ -8747,7 +8747,7 @@
         <v>59</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.292448825932801</v>
+        <v>-0.290543601573988</v>
       </c>
       <c r="D53" t="s">
         <v>56</v>
@@ -8770,7 +8770,7 @@
         <v>59</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.413585095934256</v>
+        <v>-0.410890701806659</v>
       </c>
       <c r="D54" t="s">
         <v>56</v>
@@ -8793,7 +8793,7 @@
         <v>59</v>
       </c>
       <c r="C55" t="n">
-        <v>2.31912485238972</v>
+        <v>2.34642159589753</v>
       </c>
       <c r="D55" t="s">
         <v>56</v>
@@ -8816,7 +8816,7 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>1.07863874326001</v>
+        <v>1.10237567838045</v>
       </c>
       <c r="D56" t="s">
         <v>56</v>
@@ -8839,7 +8839,7 @@
         <v>59</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.249763721003041</v>
+        <v>-0.236595342256258</v>
       </c>
       <c r="D57" t="s">
         <v>56</v>
@@ -8862,7 +8862,7 @@
         <v>59</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.05443923734996</v>
+        <v>-1.04756985323299</v>
       </c>
       <c r="D58" t="s">
         <v>56</v>
@@ -8885,7 +8885,7 @@
         <v>59</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.01307245025896</v>
+        <v>-1.00647255948039</v>
       </c>
       <c r="D59" t="s">
         <v>56</v>
@@ -8908,7 +8908,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.43270079882276</v>
+        <v>-1.45271800786994</v>
       </c>
       <c r="D60" t="s">
         <v>56</v>
@@ -8931,7 +8931,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.249763721003041</v>
+        <v>-0.236595342256258</v>
       </c>
       <c r="D61" t="s">
         <v>56</v>
@@ -8954,7 +8954,7 @@
         <v>59</v>
       </c>
       <c r="C62" t="n">
-        <v>0.37116611173587</v>
+        <v>0.31276705293585</v>
       </c>
       <c r="D62" t="s">
         <v>56</v>
@@ -8977,7 +8977,7 @@
         <v>59</v>
       </c>
       <c r="C63" t="n">
-        <v>0.539905524799017</v>
+        <v>0.558737695334593</v>
       </c>
       <c r="D63" t="s">
         <v>56</v>
@@ -9000,7 +9000,7 @@
         <v>59</v>
       </c>
       <c r="C64" t="n">
-        <v>0.51866548068672</v>
+        <v>0.532181156390174</v>
       </c>
       <c r="D64" t="s">
         <v>56</v>
@@ -9023,7 +9023,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.362738125055006</v>
+        <v>-0.360374985078224</v>
       </c>
       <c r="D65" t="s">
         <v>56</v>
@@ -9046,7 +9046,7 @@
         <v>60</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.512989176042577</v>
+        <v>-0.509647191437626</v>
       </c>
       <c r="D66" t="s">
         <v>56</v>
@@ -9069,7 +9069,7 @@
         <v>60</v>
       </c>
       <c r="C67" t="n">
-        <v>0.596480908063461</v>
+        <v>0.615387112882045</v>
       </c>
       <c r="D67" t="s">
         <v>56</v>
@@ -9092,7 +9092,7 @@
         <v>60</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.948683298050514</v>
+        <v>-0.934235315874542</v>
       </c>
       <c r="D68" t="s">
         <v>56</v>
@@ -9115,7 +9115,7 @@
         <v>60</v>
       </c>
       <c r="C69" t="n">
-        <v>0.730536933033721</v>
+        <v>0.753692210422761</v>
       </c>
       <c r="D69" t="s">
         <v>56</v>
@@ -9138,7 +9138,7 @@
         <v>60</v>
       </c>
       <c r="C70" t="n">
-        <v>0.985933454817279</v>
+        <v>1.00949537843465</v>
       </c>
       <c r="D70" t="s">
         <v>56</v>
@@ -9161,7 +9161,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="n">
-        <v>1.13090555238758</v>
+        <v>1.15474740027486</v>
       </c>
       <c r="D71" t="s">
         <v>56</v>
@@ -9184,7 +9184,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="n">
-        <v>1.03661053607841</v>
+        <v>0.973012459711204</v>
       </c>
       <c r="D72" t="s">
         <v>56</v>
@@ -9207,7 +9207,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.693073500570453</v>
+        <v>-0.679253473590884</v>
       </c>
       <c r="D73" t="s">
         <v>56</v>
@@ -9230,7 +9230,7 @@
         <v>60</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8891812384738</v>
+        <v>-0.934235315874542</v>
       </c>
       <c r="D74" t="s">
         <v>56</v>
@@ -9253,7 +9253,7 @@
         <v>60</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.45095250022002</v>
+        <v>-1.44149994031289</v>
       </c>
       <c r="D75" t="s">
         <v>56</v>
@@ -9276,7 +9276,7 @@
         <v>60</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0822612745660623</v>
+        <v>0.0953462589245593</v>
       </c>
       <c r="D76" t="s">
         <v>56</v>
@@ -9330,7 +9330,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>2.75776415922296</v>
+        <v>2.78008922588756</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -9347,7 +9347,7 @@
         <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>2.31912485238972</v>
+        <v>2.34642159589753</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
@@ -9364,7 +9364,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>4.23850354260814</v>
+        <v>3.83761289440099</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -9381,7 +9381,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2.59720497539384</v>
+        <v>2.51604243415518</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
@@ -9435,7 +9435,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0178519173042516</v>
+        <v>0.0152015560827021</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -9461,7 +9461,7 @@
         <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>0.333630904665438</v>
+        <v>0.31200584504614</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -9518,7 +9518,7 @@
         <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>0.223495463127238</v>
+        <v>0.229045093443248</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
@@ -9541,7 +9541,7 @@
         <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.117031888138647</v>
+        <v>-0.143189003577837</v>
       </c>
       <c r="D3" t="s">
         <v>64</v>
@@ -9564,7 +9564,7 @@
         <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.00638901518160475</v>
+        <v>-0.00219849911032895</v>
       </c>
       <c r="D4" t="s">
         <v>64</v>
@@ -9587,7 +9587,7 @@
         <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0779866236930613</v>
+        <v>-0.0742194042720538</v>
       </c>
       <c r="D5" t="s">
         <v>64</v>
@@ -9610,7 +9610,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.595665410724426</v>
+        <v>-0.594958792083545</v>
       </c>
       <c r="D6" t="s">
         <v>64</v>
@@ -9633,7 +9633,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0418368507681592</v>
+        <v>-0.0378559080384378</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
@@ -9656,7 +9656,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0678270043222406</v>
+        <v>-0.0639997195870825</v>
       </c>
       <c r="D8" t="s">
         <v>64</v>
@@ -9679,7 +9679,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.159879313166949</v>
+        <v>-0.156596256581216</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
@@ -9702,7 +9702,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.212029657727519</v>
+        <v>-0.209054922419853</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -9725,7 +9725,7 @@
         <v>63</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0467534908091291</v>
+        <v>0.0512581939774382</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
@@ -9748,7 +9748,7 @@
         <v>63</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0202230302248723</v>
+        <v>-0.0283237294140919</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>
@@ -9771,7 +9771,7 @@
         <v>63</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0476863285877227</v>
+        <v>-0.0437399689176637</v>
       </c>
       <c r="D13" t="s">
         <v>64</v>
@@ -9794,7 +9794,7 @@
         <v>63</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0869686508186277</v>
+        <v>0.06997105601045</v>
       </c>
       <c r="D14" t="s">
         <v>64</v>
@@ -9817,7 +9817,7 @@
         <v>63</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0174445282605797</v>
+        <v>-0.0133193741720659</v>
       </c>
       <c r="D15" t="s">
         <v>64</v>
@@ -9840,7 +9840,7 @@
         <v>63</v>
       </c>
       <c r="C16" t="n">
-        <v>1.06917954069218</v>
+        <v>1.0797289921567</v>
       </c>
       <c r="D16" t="s">
         <v>64</v>
